--- a/example_cases.xlsx
+++ b/example_cases.xlsx
@@ -1,52 +1,145 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузки\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD5F19D-6749-4F55-9CF2-422D9D06CA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Обращения" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Другой формат" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Обращения" sheetId="1" r:id="rId1"/>
+    <sheet name="Другой формат" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Обращения'!$A$1:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Другой формат'!$A$3:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Обращения!$B$1:$D$5</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+  <si>
+    <t>Дата</t>
+  </si>
+  <si>
+    <t>Фраза</t>
+  </si>
+  <si>
+    <t>Интент</t>
+  </si>
+  <si>
+    <t>Комментарий</t>
+  </si>
+  <si>
+    <t>Банкомат не выдал деньги</t>
+  </si>
+  <si>
+    <t>Проблема с выдачей наличных</t>
+  </si>
+  <si>
+    <t>Деньги списались со счета</t>
+  </si>
+  <si>
+    <t>Перенести платеж по кредиту</t>
+  </si>
+  <si>
+    <t>Изменение даты платежа</t>
+  </si>
+  <si>
+    <t>Клиент просит изменить день списания</t>
+  </si>
+  <si>
+    <t>Проверка операции</t>
+  </si>
+  <si>
+    <t>Повторное обращение, другой кейс</t>
+  </si>
+  <si>
+    <t>Заказать справку о доходах</t>
+  </si>
+  <si>
+    <t>Документы и справки</t>
+  </si>
+  <si>
+    <t>Примеры обращений — заголовки начинаются в строке 3</t>
+  </si>
+  <si>
+    <t>Запрос</t>
+  </si>
+  <si>
+    <t>Категория</t>
+  </si>
+  <si>
+    <t>Ссылка</t>
+  </si>
+  <si>
+    <t>Описание</t>
+  </si>
+  <si>
+    <t>Не приходит код подтверждения</t>
+  </si>
+  <si>
+    <t>Вход в приложение</t>
+  </si>
+  <si>
+    <t>https://example.org/help</t>
+  </si>
+  <si>
+    <t>Клиент не получает СМС</t>
+  </si>
+  <si>
+    <t>Где найти выписку</t>
+  </si>
+  <si>
+    <t>Документы</t>
+  </si>
+  <si>
+    <t>https://example.org/statements</t>
+  </si>
+  <si>
+    <t>Выписка по счету</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006241A5"/>
+        <fgColor rgb="FF6241A5"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,87 +156,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -431,215 +465,148 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Дата</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Фраза</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Интент</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2">
         <v>46301</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Банкомат не выдал деньги</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Проблема с выдачей наличных</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Деньги списались со счета</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2">
         <v>46301</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Перенести платеж по кредиту</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Изменение даты платежа</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Клиент просит изменить день списания</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
         <v>46302</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Банкомат не выдал деньги</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Проверка операции</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Повторное обращение, другой кейс</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2">
         <v>46302</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Заказать справку о доходах</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Документы и справки</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Примеры обращений — заголовки начинаются в строке 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Запрос</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Категория</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Ссылка</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Описание</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Не приходит код подтверждения</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Вход в приложение</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>https://example.org/help</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Клиент не получает СМС</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Где найти выписку</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Документы</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>https://example.org/statements</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Выписка по счету</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D5"/>
+  <autoFilter ref="A3:D5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/example_cases.xlsx
+++ b/example_cases.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD5F19D-6749-4F55-9CF2-422D9D06CA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC7C2FD-9BFD-4821-92E0-062E9A8BA945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Обращения" sheetId="1" r:id="rId1"/>
     <sheet name="Другой формат" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Другой формат'!$A$3:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Другой формат'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Обращения!$B$1:$D$5</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>Документы и справки</t>
-  </si>
-  <si>
-    <t>Примеры обращений — заголовки начинаются в строке 3</t>
   </si>
   <si>
     <t>Запрос</t>
@@ -549,7 +546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -559,54 +556,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:D3" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>